--- a/data/trans_camb/P23_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P23_R-Estudios-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,42; 2,51</t>
+          <t>-5,94; 2,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,81; -2,19</t>
+          <t>-10,7; -1,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 4,26</t>
+          <t>-1,14; 4,12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 3,31</t>
+          <t>-2,34; 3,44</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 2,25</t>
+          <t>-2,69; 2,08</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,5; -0,36</t>
+          <t>-5,24; 0,01</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-17,18; 7,3</t>
+          <t>-15,61; 8,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-28,3; -6,53</t>
+          <t>-28,23; -4,95</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-9,07; 35,04</t>
+          <t>-7,86; 33,77</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-15,72; 26,82</t>
+          <t>-15,96; 27,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-12,23; 10,0</t>
+          <t>-11,09; 9,46</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-22,45; -1,65</t>
+          <t>-21,65; -0,17</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,09; -1,41</t>
+          <t>-8,17; -1,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,19; -5,82</t>
+          <t>-12,36; -5,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 4,74</t>
+          <t>-1,82; 5,18</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 1,53</t>
+          <t>-4,36; 1,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 0,76</t>
+          <t>-3,77; 1,12</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,53; -2,94</t>
+          <t>-7,7; -2,89</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-16,16; -3,02</t>
+          <t>-16,29; -3,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-24,22; -12,48</t>
+          <t>-24,93; -12,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 14,45</t>
+          <t>-5,12; 16,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-11,84; 4,64</t>
+          <t>-11,97; 5,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-9,11; 1,91</t>
+          <t>-8,88; 2,73</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-17,5; -7,19</t>
+          <t>-18,01; -7,16</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,35; 5,18</t>
+          <t>-6,76; 4,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-15,35; -3,8</t>
+          <t>-14,75; -3,4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 7,61</t>
+          <t>-5,3; 7,55</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-12,02; -1,04</t>
+          <t>-12,53; -1,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 3,91</t>
+          <t>-4,66; 4,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,15; -4,52</t>
+          <t>-12,4; -4,4</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-19,36; 16,35</t>
+          <t>-18,45; 15,3</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-40,63; -11,79</t>
+          <t>-40,28; -11,28</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-16,73; 29,6</t>
+          <t>-15,96; 29,45</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-37,95; -4,04</t>
+          <t>-38,65; -4,76</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-13,35; 12,52</t>
+          <t>-13,82; 13,4</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-35,31; -13,6</t>
+          <t>-35,83; -14,15</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,17; -0,21</t>
+          <t>-5,44; -0,48</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,74; -5,1</t>
+          <t>-9,86; -5,01</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 4,26</t>
+          <t>-0,17; 4,08</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 2,93</t>
+          <t>-1,56; 2,79</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 1,24</t>
+          <t>-2,17; 1,28</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,99; -1,71</t>
+          <t>-4,88; -1,62</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-12,03; -0,53</t>
+          <t>-12,49; -1,21</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-22,16; -12,3</t>
+          <t>-22,74; -12,2</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 17,04</t>
+          <t>-0,53; 16,9</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-5,8; 11,82</t>
+          <t>-5,91; 11,34</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-6,04; 3,85</t>
+          <t>-6,3; 3,91</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-14,35; -5,2</t>
+          <t>-14,19; -4,86</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P23_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P23_R-Estudios-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,94; 2,78</t>
+          <t>-6,57; 2,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,7; -1,6</t>
+          <t>-11,02; -2,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 4,12</t>
+          <t>-1,29; 4,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 3,44</t>
+          <t>-2,71; 3,2</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 2,08</t>
+          <t>-2,87; 2,09</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 0,01</t>
+          <t>-5,37; -0,05</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-15,61; 8,23</t>
+          <t>-17,13; 6,05</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-28,23; -4,95</t>
+          <t>-28,45; -5,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-7,86; 33,77</t>
+          <t>-8,58; 35,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-15,96; 27,88</t>
+          <t>-18,5; 26,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-11,09; 9,46</t>
+          <t>-11,74; 9,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-21,65; -0,17</t>
+          <t>-21,32; -0,07</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,17; -1,61</t>
+          <t>-7,95; -1,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,36; -5,56</t>
+          <t>-12,19; -5,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 5,18</t>
+          <t>-1,9; 4,92</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 1,93</t>
+          <t>-4,71; 1,81</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 1,12</t>
+          <t>-3,73; 1,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,7; -2,89</t>
+          <t>-7,53; -2,86</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-16,29; -3,42</t>
+          <t>-15,92; -2,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-24,93; -12,31</t>
+          <t>-24,39; -11,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 16,0</t>
+          <t>-5,01; 14,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-11,97; 5,99</t>
+          <t>-13,07; 5,53</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-8,88; 2,73</t>
+          <t>-8,96; 2,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-18,01; -7,16</t>
+          <t>-17,6; -6,93</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,76; 4,8</t>
+          <t>-7,44; 4,84</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-14,75; -3,4</t>
+          <t>-14,86; -3,87</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 7,55</t>
+          <t>-4,51; 7,55</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-12,53; -1,45</t>
+          <t>-12,68; -1,47</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 4,0</t>
+          <t>-4,54; 4,38</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,4; -4,4</t>
+          <t>-12,19; -4,62</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-18,45; 15,3</t>
+          <t>-19,69; 15,26</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-40,28; -11,28</t>
+          <t>-39,86; -11,66</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-15,96; 29,45</t>
+          <t>-14,38; 29,1</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-38,65; -4,76</t>
+          <t>-39,06; -5,38</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-13,82; 13,4</t>
+          <t>-13,37; 14,52</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-35,83; -14,15</t>
+          <t>-36,04; -15,55</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,44; -0,48</t>
+          <t>-5,37; -0,42</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,86; -5,01</t>
+          <t>-9,7; -5,01</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 4,08</t>
+          <t>-0,28; 4,27</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 2,79</t>
+          <t>-1,78; 2,63</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 1,28</t>
+          <t>-2,02; 1,2</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,88; -1,62</t>
+          <t>-5,03; -1,78</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-12,49; -1,21</t>
+          <t>-12,29; -1,04</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-22,74; -12,2</t>
+          <t>-22,43; -12,3</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 16,9</t>
+          <t>-1,04; 17,61</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-5,91; 11,34</t>
+          <t>-6,78; 10,73</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-6,3; 3,91</t>
+          <t>-5,87; 3,63</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-14,19; -4,86</t>
+          <t>-14,35; -5,37</t>
         </is>
       </c>
     </row>
